--- a/System Design Fundamentals.xlsx
+++ b/System Design Fundamentals.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="10" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Networking" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Distributed System" sheetId="4" r:id="rId4"/>
     <sheet name="Distributed Databases" sheetId="5" r:id="rId5"/>
     <sheet name="Messaging &amp; Events" sheetId="6" r:id="rId6"/>
-    <sheet name="API Desing" sheetId="7" r:id="rId7"/>
+    <sheet name="API Design" sheetId="7" r:id="rId7"/>
     <sheet name="MicroServices" sheetId="8" r:id="rId8"/>
     <sheet name="Observability" sheetId="9" r:id="rId9"/>
     <sheet name="Security" sheetId="10" r:id="rId10"/>

--- a/System Design Fundamentals.xlsx
+++ b/System Design Fundamentals.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="10" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="10" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Networking" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="321">
   <si>
     <t>Webhooks</t>
   </si>
@@ -981,6 +981,21 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/alexxubyte_systemdesign-coding-interviewtips-share-7436445893542801409-YVJI/</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=f69hh3KgFEk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Bay3X9PAX5k</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ibxXO-b14j4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ol-FaNLXlR0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FaTB91EQGzM</t>
   </si>
 </sst>
 </file>
@@ -1896,68 +1911,91 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B1" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>248</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B1" r:id="rId2"/>
+    <hyperlink ref="B3" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B4" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
